--- a/dependency-matrix.xlsx
+++ b/dependency-matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://capgemini-my.sharepoint.com/personal/nicketa_nicketa_capgemini_com/Documents/Work/2. POC/Specathon/Scrum-Master/Scrum-Master/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="11_F25DC773A252ABDACC104886619B6F9A5BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9504BE8F-9D11-407B-98E8-CACC18609534}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="11_F25DC773A252ABDACC104886619B6F9A5BDE58E9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41F6B94F-DC13-4BB2-8E5B-EABDF011A768}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,10 +66,10 @@
     <t>Manish</t>
   </si>
   <si>
-    <t>Sanjot</t>
-  </si>
-  <si>
     <t>Low</t>
+  </si>
+  <si>
+    <t>None</t>
   </si>
 </sst>
 </file>
@@ -453,10 +453,10 @@
         <v>12</v>
       </c>
       <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
         <v>13</v>
-      </c>
-      <c r="D4" t="s">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
